--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/5536-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/5536-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{99316417-EA5A-44DE-BD5D-78E4E8704A4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EBA2D8EE-A14B-4E04-8D38-E4B09921476C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{DCAD0FE7-F5FA-4E99-947E-3E84DB32E1D5}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{3257C2C5-6E28-4035-B797-CC5A8D346E2C}"/>
   </bookViews>
   <sheets>
     <sheet name="5536-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1549,30 +1549,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C4B34C5-D872-44DC-98D6-0345D4C6F57E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C79D0A1B-7C48-4FFA-B7D8-81EA054A7457}">
   <dimension ref="A1:X31"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11.125" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="6" width="7.125" customWidth="1"/>
-    <col min="7" max="9" width="6.75" customWidth="1"/>
-    <col min="10" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="14" width="7.125" customWidth="1"/>
-    <col min="15" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.75" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="6" width="6.109375" customWidth="1"/>
+    <col min="7" max="9" width="5.88671875" customWidth="1"/>
+    <col min="10" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" customWidth="1"/>
+    <col min="15" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1606,7 +1606,7 @@
       <c r="W1" s="32"/>
       <c r="X1" s="24"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1642,7 +1642,7 @@
       <c r="W2" s="34"/>
       <c r="X2" s="35"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="X3" s="38"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1762,7 +1762,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="39">
         <v>2025</v>
       </c>
@@ -1834,7 +1834,7 @@
         <v>1.85</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1870,7 +1870,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>30</v>
       </c>
@@ -1944,7 +1944,7 @@
         <v>0.92</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="49">
         <v>2024</v>
       </c>
@@ -2016,7 +2016,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
         <v>30</v>
       </c>
@@ -2090,7 +2090,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="18" t="s">
         <v>30</v>
       </c>
@@ -2164,7 +2164,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="51">
         <v>2023</v>
       </c>
@@ -2236,7 +2236,7 @@
         <v>6.09</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>30</v>
       </c>
@@ -2310,7 +2310,7 @@
         <v>3.48</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>30</v>
       </c>
@@ -2384,7 +2384,7 @@
         <v>2.61</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="49">
         <v>2022</v>
       </c>
@@ -2456,7 +2456,7 @@
         <v>11.6</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
         <v>30</v>
       </c>
@@ -2530,7 +2530,7 @@
         <v>8.2200000000000006</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="18" t="s">
         <v>30</v>
       </c>
@@ -2604,7 +2604,7 @@
         <v>3.41</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="51">
         <v>2021</v>
       </c>
@@ -2676,7 +2676,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="49">
         <v>2020</v>
       </c>
@@ -2748,7 +2748,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="51">
         <v>2019</v>
       </c>
@@ -2820,7 +2820,7 @@
         <v>9.49</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="49">
         <v>2018</v>
       </c>
@@ -2892,7 +2892,7 @@
         <v>9.9700000000000006</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="51">
         <v>2017</v>
       </c>
@@ -2964,7 +2964,7 @@
         <v>9.73</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="49">
         <v>2016</v>
       </c>
@@ -3036,7 +3036,7 @@
         <v>8.7100000000000009</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="51">
         <v>2015</v>
       </c>
@@ -3108,7 +3108,7 @@
         <v>7.88</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="49">
         <v>2014</v>
       </c>
@@ -3180,7 +3180,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="51">
         <v>2013</v>
       </c>
@@ -3252,7 +3252,7 @@
         <v>13.9</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="49">
         <v>2012</v>
       </c>
@@ -3324,7 +3324,7 @@
         <v>8.6999999999999993</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="51">
         <v>2011</v>
       </c>
@@ -3396,7 +3396,7 @@
         <v>10.7</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="49">
         <v>2010</v>
       </c>
@@ -3468,7 +3468,7 @@
         <v>11.2</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="51">
         <v>2009</v>
       </c>
@@ -3540,7 +3540,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="49">
         <v>2008</v>
       </c>
@@ -3612,7 +3612,7 @@
         <v>2.86</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="51" t="s">
         <v>54</v>
       </c>
